--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3646-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3646-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C2A1E3C-0040-4E96-B65C-786F59EB442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{559330BF-32CB-4424-AD5B-A3F456D6B400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C235924B-793D-4BC6-A9C6-EDE14934C83A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B52E9CA9-40F3-4D98-9147-94B422C48CCA}"/>
   </bookViews>
   <sheets>
     <sheet name="3646-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
   <si>
     <t>股利</t>
   </si>
@@ -37,7 +37,7 @@
     <t>股利政策</t>
   </si>
   <si>
-    <t>現金殖利率</t>
+    <t>現金+股票殖利率</t>
   </si>
   <si>
     <t>股東股利 (元/股)</t>
@@ -70,7 +70,7 @@
     <t>年度</t>
   </si>
   <si>
-    <t>除息前</t>
+    <t>除權/息前</t>
   </si>
   <si>
     <t>年均價</t>
@@ -91,10 +91,16 @@
     <t>公積</t>
   </si>
   <si>
+    <t>除息</t>
+  </si>
+  <si>
+    <t>除權</t>
+  </si>
+  <si>
+    <t>利率</t>
+  </si>
+  <si>
     <t>價格</t>
-  </si>
-  <si>
-    <t>利率</t>
   </si>
   <si>
     <t> '25/08/26 </t>
@@ -1451,27 +1457,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF59DF0-F9D0-4E67-A48A-5B132F4B2C74}">
-  <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C21068-26D8-43B6-B543-67298F5077A7}">
+  <dimension ref="A1:X22"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.375" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.375" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="17" width="6.375" customWidth="1"/>
-    <col min="18" max="18" width="6.625" customWidth="1"/>
-    <col min="19" max="19" width="6.375" customWidth="1"/>
-    <col min="20" max="20" width="6.625" customWidth="1"/>
-    <col min="21" max="21" width="6.375" customWidth="1"/>
-    <col min="22" max="22" width="6.625" customWidth="1"/>
-    <col min="23" max="23" width="7.625" customWidth="1"/>
+    <col min="1" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="6" width="7.88671875" customWidth="1"/>
+    <col min="7" max="9" width="7.5546875" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" customWidth="1"/>
+    <col min="11" max="13" width="7.5546875" customWidth="1"/>
+    <col min="14" max="15" width="7.88671875" customWidth="1"/>
+    <col min="16" max="18" width="7.5546875" customWidth="1"/>
+    <col min="19" max="19" width="7.88671875" customWidth="1"/>
+    <col min="20" max="20" width="7.5546875" customWidth="1"/>
+    <col min="21" max="21" width="7.88671875" customWidth="1"/>
+    <col min="22" max="22" width="7.5546875" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1502,9 +1508,10 @@
       <c r="T1" s="26"/>
       <c r="U1" s="26"/>
       <c r="V1" s="26"/>
-      <c r="W1" s="18"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1537,9 +1544,10 @@
       <c r="T2" s="28"/>
       <c r="U2" s="28"/>
       <c r="V2" s="28"/>
-      <c r="W2" s="29"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1572,25 +1580,26 @@
       <c r="N3" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="30" t="s">
+      <c r="O3" s="31"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="30" t="s">
+      <c r="R3" s="32"/>
+      <c r="S3" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="32"/>
-      <c r="T3" s="30" t="s">
+      <c r="T3" s="32"/>
+      <c r="U3" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="30" t="s">
+      <c r="V3" s="32"/>
+      <c r="W3" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1631,37 +1640,40 @@
         <v>24</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
       <c r="B5" s="34"/>
       <c r="C5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="10">
         <v>1.65</v>
@@ -1688,7 +1700,7 @@
         <v>12</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M5" s="11">
         <v>2025</v>
@@ -1696,41 +1708,44 @@
       <c r="N5" s="12">
         <v>29.4</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="10">
         <v>5.61</v>
       </c>
-      <c r="P5" s="12">
+      <c r="Q5" s="12">
         <v>28.8</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="R5" s="10">
         <v>5.73</v>
       </c>
-      <c r="R5" s="12">
+      <c r="S5" s="12">
         <v>24.3</v>
       </c>
-      <c r="S5" s="10">
+      <c r="T5" s="10">
         <v>6.79</v>
       </c>
-      <c r="T5" s="12">
+      <c r="U5" s="12">
         <v>30.85</v>
       </c>
-      <c r="U5" s="10">
+      <c r="V5" s="10">
         <v>5.35</v>
       </c>
-      <c r="V5" s="12">
+      <c r="W5" s="12">
         <v>24</v>
       </c>
-      <c r="W5" s="10">
+      <c r="X5" s="10">
         <v>6.88</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
       <c r="B6" s="36"/>
       <c r="C6" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="14">
         <v>1.5</v>
@@ -1757,7 +1772,7 @@
         <v>20</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M6" s="15">
         <v>2024</v>
@@ -1765,41 +1780,44 @@
       <c r="N6" s="16">
         <v>30.7</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="14">
         <v>4.8899999999999997</v>
       </c>
-      <c r="P6" s="16">
+      <c r="Q6" s="16">
         <v>30.1</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="R6" s="14">
         <v>4.9800000000000004</v>
       </c>
-      <c r="R6" s="16">
+      <c r="S6" s="16">
         <v>29.1</v>
       </c>
-      <c r="S6" s="14">
+      <c r="T6" s="14">
         <v>5.15</v>
       </c>
-      <c r="T6" s="16">
+      <c r="U6" s="16">
         <v>32.1</v>
       </c>
-      <c r="U6" s="14">
+      <c r="V6" s="14">
         <v>4.67</v>
       </c>
-      <c r="V6" s="16">
+      <c r="W6" s="16">
         <v>27.05</v>
       </c>
-      <c r="W6" s="14">
+      <c r="X6" s="14">
         <v>5.55</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
       <c r="B7" s="34"/>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" s="10">
         <v>2.0699999999999998</v>
@@ -1826,7 +1844,7 @@
         <v>102</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M7" s="11">
         <v>2023</v>
@@ -1834,41 +1852,44 @@
       <c r="N7" s="12">
         <v>29.7</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="10">
         <v>6.97</v>
       </c>
-      <c r="P7" s="12">
+      <c r="Q7" s="12">
         <v>28.2</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="R7" s="10">
         <v>7.34</v>
       </c>
-      <c r="R7" s="12">
+      <c r="S7" s="12">
         <v>28.45</v>
       </c>
-      <c r="S7" s="10">
+      <c r="T7" s="10">
         <v>7.27</v>
       </c>
-      <c r="T7" s="12">
+      <c r="U7" s="12">
         <v>38.5</v>
       </c>
-      <c r="U7" s="10">
+      <c r="V7" s="10">
         <v>5.38</v>
       </c>
-      <c r="V7" s="12">
+      <c r="W7" s="12">
         <v>23</v>
       </c>
-      <c r="W7" s="10">
+      <c r="X7" s="10">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="14">
         <v>1.677</v>
@@ -1895,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M8" s="15">
         <v>2022</v>
@@ -1903,41 +1924,44 @@
       <c r="N8" s="16">
         <v>26.9</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="14">
         <v>6.24</v>
       </c>
-      <c r="P8" s="16">
+      <c r="Q8" s="16">
         <v>25.3</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="R8" s="14">
         <v>6.62</v>
       </c>
-      <c r="R8" s="16">
+      <c r="S8" s="16">
         <v>23.3</v>
       </c>
-      <c r="S8" s="14">
+      <c r="T8" s="14">
         <v>7.2</v>
       </c>
-      <c r="T8" s="16">
+      <c r="U8" s="16">
         <v>31.65</v>
       </c>
-      <c r="U8" s="14">
+      <c r="V8" s="14">
         <v>5.3</v>
       </c>
-      <c r="V8" s="16">
+      <c r="W8" s="16">
         <v>20</v>
       </c>
-      <c r="W8" s="14">
+      <c r="X8" s="14">
         <v>8.39</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="10">
         <v>0.92300000000000004</v>
@@ -1964,7 +1988,7 @@
         <v>28</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="11">
         <v>2021</v>
@@ -1972,41 +1996,44 @@
       <c r="N9" s="12">
         <v>27.95</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="10">
         <v>3.3</v>
       </c>
-      <c r="P9" s="12">
+      <c r="Q9" s="12">
         <v>26</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="R9" s="10">
         <v>3.55</v>
       </c>
-      <c r="R9" s="12">
+      <c r="S9" s="12">
         <v>28.75</v>
       </c>
-      <c r="S9" s="10">
+      <c r="T9" s="10">
         <v>3.21</v>
       </c>
-      <c r="T9" s="12">
+      <c r="U9" s="12">
         <v>34.200000000000003</v>
       </c>
-      <c r="U9" s="10">
+      <c r="V9" s="10">
         <v>2.7</v>
       </c>
-      <c r="V9" s="12">
+      <c r="W9" s="12">
         <v>20.75</v>
       </c>
-      <c r="W9" s="10">
+      <c r="X9" s="10">
         <v>4.45</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
       <c r="B10" s="36"/>
       <c r="C10" s="15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="14">
         <v>0.56899999999999995</v>
@@ -2033,7 +2060,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M10" s="15">
         <v>2020</v>
@@ -2041,41 +2068,44 @@
       <c r="N10" s="16">
         <v>17.5</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="14">
         <v>4.8600000000000003</v>
       </c>
-      <c r="P10" s="16">
+      <c r="Q10" s="16">
         <v>17.600000000000001</v>
       </c>
-      <c r="Q10" s="14">
+      <c r="R10" s="14">
         <v>4.84</v>
       </c>
-      <c r="R10" s="16">
+      <c r="S10" s="16">
         <v>21.25</v>
       </c>
-      <c r="S10" s="14">
+      <c r="T10" s="14">
         <v>4</v>
       </c>
-      <c r="T10" s="16">
+      <c r="U10" s="16">
         <v>24.3</v>
       </c>
-      <c r="U10" s="14">
+      <c r="V10" s="14">
         <v>3.5</v>
       </c>
-      <c r="V10" s="16">
+      <c r="W10" s="16">
         <v>11.8</v>
       </c>
-      <c r="W10" s="14">
+      <c r="X10" s="14">
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
       <c r="B11" s="34"/>
       <c r="C11" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D11" s="10">
         <v>0.96899999999999997</v>
@@ -2102,7 +2132,7 @@
         <v>50</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M11" s="11">
         <v>2019</v>
@@ -2110,41 +2140,44 @@
       <c r="N11" s="12">
         <v>18.8</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="10">
         <v>5.3</v>
       </c>
-      <c r="P11" s="12">
+      <c r="Q11" s="12">
         <v>18.2</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="R11" s="10">
         <v>5.48</v>
       </c>
-      <c r="R11" s="12">
+      <c r="S11" s="12">
         <v>17.05</v>
       </c>
-      <c r="S11" s="10">
+      <c r="T11" s="10">
         <v>5.85</v>
       </c>
-      <c r="T11" s="12">
+      <c r="U11" s="12">
         <v>21.25</v>
       </c>
-      <c r="U11" s="10">
+      <c r="V11" s="10">
         <v>4.6900000000000004</v>
       </c>
-      <c r="V11" s="12">
+      <c r="W11" s="12">
         <v>16.5</v>
       </c>
-      <c r="W11" s="10">
+      <c r="X11" s="10">
         <v>6.04</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D12" s="14">
         <v>0.628</v>
@@ -2171,7 +2204,7 @@
         <v>112</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M12" s="15">
         <v>2018</v>
@@ -2179,41 +2212,44 @@
       <c r="N12" s="16">
         <v>19.75</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="14">
         <v>5.0599999999999996</v>
       </c>
-      <c r="P12" s="16">
+      <c r="Q12" s="16">
         <v>18.8</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="R12" s="14">
         <v>5.33</v>
       </c>
-      <c r="R12" s="16">
+      <c r="S12" s="16">
         <v>17.25</v>
       </c>
-      <c r="S12" s="14">
+      <c r="T12" s="14">
         <v>5.8</v>
       </c>
-      <c r="T12" s="16">
+      <c r="U12" s="16">
         <v>29.3</v>
       </c>
-      <c r="U12" s="14">
+      <c r="V12" s="14">
         <v>3.41</v>
       </c>
-      <c r="V12" s="16">
+      <c r="W12" s="16">
         <v>14.15</v>
       </c>
-      <c r="W12" s="14">
+      <c r="X12" s="14">
         <v>7.07</v>
       </c>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
       <c r="B13" s="34"/>
       <c r="C13" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" s="10">
         <v>0.99199999999999999</v>
@@ -2240,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M13" s="11">
         <v>2017</v>
@@ -2248,41 +2284,44 @@
       <c r="N13" s="12">
         <v>20.95</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="10">
         <v>4.7300000000000004</v>
       </c>
-      <c r="P13" s="12">
+      <c r="Q13" s="12">
         <v>22.3</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="R13" s="10">
         <v>4.45</v>
       </c>
-      <c r="R13" s="12">
+      <c r="S13" s="12">
         <v>17.399999999999999</v>
       </c>
-      <c r="S13" s="10">
+      <c r="T13" s="10">
         <v>5.7</v>
       </c>
-      <c r="T13" s="12">
+      <c r="U13" s="12">
         <v>29.5</v>
       </c>
-      <c r="U13" s="10">
+      <c r="V13" s="10">
         <v>3.36</v>
       </c>
-      <c r="V13" s="12">
+      <c r="W13" s="12">
         <v>17</v>
       </c>
-      <c r="W13" s="10">
+      <c r="X13" s="10">
         <v>5.83</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="14">
         <v>0</v>
@@ -2309,7 +2348,7 @@
         <v>6</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M14" s="15">
         <v>2016</v>
@@ -2317,41 +2356,44 @@
       <c r="N14" s="16">
         <v>18.8</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="14">
         <v>5.32</v>
       </c>
-      <c r="P14" s="16">
+      <c r="Q14" s="16">
         <v>15.1</v>
       </c>
-      <c r="Q14" s="14">
+      <c r="R14" s="14">
         <v>6.6</v>
       </c>
-      <c r="R14" s="16">
+      <c r="S14" s="16">
         <v>24.9</v>
       </c>
-      <c r="S14" s="14">
+      <c r="T14" s="14">
         <v>4.0199999999999996</v>
       </c>
-      <c r="T14" s="16">
+      <c r="U14" s="16">
         <v>25.3</v>
       </c>
-      <c r="U14" s="14">
+      <c r="V14" s="14">
         <v>3.95</v>
       </c>
-      <c r="V14" s="16">
+      <c r="W14" s="16">
         <v>11</v>
       </c>
-      <c r="W14" s="14">
+      <c r="X14" s="14">
         <v>9.09</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
       <c r="B15" s="34"/>
       <c r="C15" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
@@ -2378,7 +2420,7 @@
         <v>4</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M15" s="11">
         <v>2015</v>
@@ -2386,41 +2428,44 @@
       <c r="N15" s="12">
         <v>10.35</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="10">
         <v>9.66</v>
       </c>
-      <c r="P15" s="12">
+      <c r="Q15" s="12">
         <v>15.7</v>
       </c>
-      <c r="Q15" s="10">
+      <c r="R15" s="10">
         <v>6.39</v>
       </c>
-      <c r="R15" s="12">
+      <c r="S15" s="12">
         <v>12.7</v>
       </c>
-      <c r="S15" s="10">
+      <c r="T15" s="10">
         <v>7.87</v>
       </c>
-      <c r="T15" s="12">
+      <c r="U15" s="12">
         <v>23.25</v>
       </c>
-      <c r="U15" s="10">
+      <c r="V15" s="10">
         <v>4.3</v>
       </c>
-      <c r="V15" s="12">
+      <c r="W15" s="12">
         <v>8.6</v>
       </c>
-      <c r="W15" s="10">
+      <c r="X15" s="10">
         <v>11.6</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" s="14">
         <v>0.46</v>
@@ -2447,7 +2492,7 @@
         <v>4</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M16" s="15">
         <v>2014</v>
@@ -2455,41 +2500,44 @@
       <c r="N16" s="16">
         <v>16.850000000000001</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="14">
         <v>8.9</v>
       </c>
-      <c r="P16" s="16">
+      <c r="Q16" s="16">
         <v>22.6</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="R16" s="14">
         <v>6.65</v>
       </c>
-      <c r="R16" s="16">
+      <c r="S16" s="16">
         <v>16.600000000000001</v>
       </c>
-      <c r="S16" s="14">
+      <c r="T16" s="14">
         <v>9.0399999999999991</v>
       </c>
-      <c r="T16" s="16">
+      <c r="U16" s="16">
         <v>33.299999999999997</v>
       </c>
-      <c r="U16" s="14">
+      <c r="V16" s="14">
         <v>4.5</v>
       </c>
-      <c r="V16" s="16">
+      <c r="W16" s="16">
         <v>13.55</v>
       </c>
-      <c r="W16" s="14">
+      <c r="X16" s="14">
         <v>11.1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="10">
         <v>0.4</v>
@@ -2516,7 +2564,7 @@
         <v>3</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M17" s="11">
         <v>2013</v>
@@ -2524,41 +2572,44 @@
       <c r="N17" s="12">
         <v>37.799999999999997</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="10">
         <v>2.65</v>
       </c>
-      <c r="P17" s="12">
+      <c r="Q17" s="12">
         <v>35.299999999999997</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="R17" s="10">
         <v>2.83</v>
       </c>
-      <c r="R17" s="12">
+      <c r="S17" s="12">
         <v>29.25</v>
       </c>
-      <c r="S17" s="10">
+      <c r="T17" s="10">
         <v>3.42</v>
       </c>
-      <c r="T17" s="12">
+      <c r="U17" s="12">
         <v>46.2</v>
       </c>
-      <c r="U17" s="10">
+      <c r="V17" s="10">
         <v>2.16</v>
       </c>
-      <c r="V17" s="12">
+      <c r="W17" s="12">
         <v>27</v>
       </c>
-      <c r="W17" s="10">
+      <c r="X17" s="10">
         <v>3.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
       <c r="B18" s="36"/>
       <c r="C18" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
@@ -2585,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M18" s="15">
         <v>2012</v>
@@ -2593,41 +2644,44 @@
       <c r="N18" s="16">
         <v>31.4</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="14">
         <v>6.37</v>
       </c>
-      <c r="P18" s="16">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="14">
+      <c r="Q18" s="16">
+        <v>28</v>
+      </c>
+      <c r="R18" s="14">
         <v>7.14</v>
       </c>
-      <c r="R18" s="16">
+      <c r="S18" s="16">
         <v>35.26</v>
       </c>
-      <c r="S18" s="14">
+      <c r="T18" s="14">
         <v>5.67</v>
       </c>
-      <c r="T18" s="16">
+      <c r="U18" s="16">
         <v>35.57</v>
       </c>
-      <c r="U18" s="14">
+      <c r="V18" s="14">
         <v>5.62</v>
       </c>
-      <c r="V18" s="16">
+      <c r="W18" s="16">
         <v>22.04</v>
       </c>
-      <c r="W18" s="14">
+      <c r="X18" s="14">
         <v>9.07</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D19" s="10">
         <v>1</v>
@@ -2662,41 +2716,44 @@
       <c r="N19" s="12">
         <v>31.85</v>
       </c>
-      <c r="O19" s="10">
-        <v>3.14</v>
-      </c>
-      <c r="P19" s="12">
+      <c r="O19" s="12">
+        <v>31.85</v>
+      </c>
+      <c r="P19" s="10">
+        <v>4.71</v>
+      </c>
+      <c r="Q19" s="12">
         <v>29.4</v>
       </c>
-      <c r="Q19" s="10">
-        <v>3.4</v>
-      </c>
-      <c r="R19" s="12">
+      <c r="R19" s="10">
+        <v>5.09</v>
+      </c>
+      <c r="S19" s="12">
         <v>23.7</v>
       </c>
-      <c r="S19" s="10">
-        <v>4.22</v>
-      </c>
-      <c r="T19" s="12">
+      <c r="T19" s="10">
+        <v>6.33</v>
+      </c>
+      <c r="U19" s="12">
         <v>38.729999999999997</v>
       </c>
-      <c r="U19" s="10">
-        <v>2.58</v>
-      </c>
-      <c r="V19" s="12">
+      <c r="V19" s="10">
+        <v>3.87</v>
+      </c>
+      <c r="W19" s="12">
         <v>14</v>
       </c>
-      <c r="W19" s="10">
-        <v>7.14</v>
+      <c r="X19" s="10">
+        <v>10.7</v>
       </c>
     </row>
-    <row r="20" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
@@ -2723,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M20" s="15">
         <v>2010</v>
@@ -2731,41 +2788,44 @@
       <c r="N20" s="16">
         <v>18.5</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="14">
         <v>5.41</v>
       </c>
-      <c r="P20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="R20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="S20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="V20" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="W20" s="14" t="s">
-        <v>26</v>
+      <c r="Q20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="S20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="W20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="X20" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
       <c r="B21" s="34"/>
       <c r="C21" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D21" s="10">
         <v>0.3</v>
@@ -2789,48 +2849,51 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M21" s="11">
         <v>2009</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="S21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="U21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="V21" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W21" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="T21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="U21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="V21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="W21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="X21" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B22" s="36"/>
       <c r="C22" s="14"/>
@@ -2868,6 +2931,7 @@
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -2887,10 +2951,10 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B1"/>
@@ -2898,11 +2962,11 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="M1:W2"/>
+    <mergeCell ref="M1:X2"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3646-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3646-dividend-20260215_1_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{559330BF-32CB-4424-AD5B-A3F456D6B400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7646F42-13E4-45D4-84C8-F1D4000D7A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{B52E9CA9-40F3-4D98-9147-94B422C48CCA}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1FBCCA7A-7FEE-44FB-A515-8B4AA000E1E3}"/>
   </bookViews>
   <sheets>
     <sheet name="3646-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1457,24 +1457,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C21068-26D8-43B6-B543-67298F5077A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59B60EE-A3BB-4D5D-B291-E3957052CE50}">
   <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="6" width="7.88671875" customWidth="1"/>
-    <col min="7" max="9" width="7.5546875" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" customWidth="1"/>
-    <col min="11" max="13" width="7.5546875" customWidth="1"/>
-    <col min="14" max="15" width="7.88671875" customWidth="1"/>
-    <col min="16" max="18" width="7.5546875" customWidth="1"/>
-    <col min="19" max="19" width="7.88671875" customWidth="1"/>
-    <col min="20" max="20" width="7.5546875" customWidth="1"/>
-    <col min="21" max="21" width="7.88671875" customWidth="1"/>
-    <col min="22" max="22" width="7.5546875" customWidth="1"/>
-    <col min="23" max="23" width="7.88671875" customWidth="1"/>
-    <col min="24" max="24" width="8.109375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
